--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FA490B-71C8-4A4F-BEBD-74BC7D73F420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D0DE76-B175-4B56-B697-8F058351AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="34" r:id="rId1"/>
+    <sheet name="FEVRIER 2026" sheetId="35" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -156,6 +157,15 @@
   <si>
     <t>16 Compteurs DN 15/21 Destination Antenne Tlathet Douairs</t>
   </si>
+  <si>
+    <t>Mois de FEVRIER 2026</t>
+  </si>
+  <si>
+    <t>2 Compteurs DN 15/21 Destination Antenne Zoubiria</t>
+  </si>
+  <si>
+    <t>1 Compteurs DN 15/21 Destination Antenne Ouled dhied</t>
+  </si>
 </sst>
 </file>
 
@@ -988,6 +998,101 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="2" borderId="41" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,101 +1101,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="2" borderId="41" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1134,6 +1144,139 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45369A9B-4B5C-45C7-BEA5-EAE54033CEF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1542,48 +1685,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="A1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -1594,36 +1737,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1635,36 +1778,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="58" t="s">
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="59" t="s">
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="76" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -1695,7 +1838,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="60"/>
+      <c r="L8" s="77"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -2570,149 +2713,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="62" t="s">
+      <c r="A42" s="60"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="63"/>
-      <c r="I42" s="63" t="s">
+      <c r="H42" s="62"/>
+      <c r="I42" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="64"/>
+      <c r="J42" s="63"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="65" t="s">
+      <c r="B43" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="67">
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="58">
         <v>447</v>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="65" t="s">
+      <c r="B44" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="66"/>
-      <c r="D44" s="66"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="66"/>
-      <c r="G44" s="71">
-        <v>0</v>
-      </c>
-      <c r="H44" s="72"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="72"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="49">
+        <v>0</v>
+      </c>
+      <c r="H44" s="50"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="50"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="73" t="s">
+      <c r="B45" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="73"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="74">
-        <v>0</v>
-      </c>
-      <c r="H45" s="75"/>
-      <c r="I45" s="67"/>
-      <c r="J45" s="76"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="56">
+        <v>0</v>
+      </c>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="59"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="65" t="s">
+      <c r="B46" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="66"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="66"/>
-      <c r="G46" s="77">
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="54">
         <f>L40+G45</f>
         <v>96</v>
       </c>
-      <c r="H46" s="72"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="72"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="50"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="66"/>
-      <c r="D47" s="66"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="77">
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="54">
         <f>G43+G44-G46</f>
         <v>351</v>
       </c>
-      <c r="H47" s="72"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="72"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="50"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="65" t="s">
+      <c r="B48" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="71">
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="49">
         <v>321</v>
       </c>
-      <c r="H48" s="72"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="72"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="50"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="65" t="s">
+      <c r="B49" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="66"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="66"/>
-      <c r="G49" s="78">
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="51">
         <f>G47-G48</f>
         <v>30</v>
       </c>
-      <c r="H49" s="79"/>
-      <c r="I49" s="80"/>
-      <c r="J49" s="79"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="52"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -2758,6 +2901,1277 @@
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="76" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="71"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="77"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="41">
+        <v>21</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21">
+        <v>5</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <v>11</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21">
+        <v>3</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <v>1</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21">
+        <v>5</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21">
+        <v>2</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21">
+        <v>2</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21">
+        <v>3</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="30">
+        <v>10</v>
+      </c>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21">
+        <v>1</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="30">
+        <v>10</v>
+      </c>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30">
+        <v>10</v>
+      </c>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30">
+        <v>4</v>
+      </c>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21">
+        <v>5</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21">
+        <v>1</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21">
+        <v>2</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>33</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>34</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>69</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="60"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="63"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="58">
+        <v>321</v>
+      </c>
+      <c r="H43" s="64"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="49">
+        <v>0</v>
+      </c>
+      <c r="H44" s="50"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="56">
+        <v>0</v>
+      </c>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="59"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="54">
+        <f>L40+G45</f>
+        <v>104</v>
+      </c>
+      <c r="H46" s="50"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="54">
+        <f>G43+G44-G46</f>
+        <v>217</v>
+      </c>
+      <c r="H47" s="50"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="49">
+        <v>214</v>
+      </c>
+      <c r="H48" s="50"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="51">
+        <f>G47-G48</f>
+        <v>3</v>
+      </c>
+      <c r="H49" s="52"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2792,12 +4206,12 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D0DE76-B175-4B56-B697-8F058351AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E864B58-C279-4C8A-BFCF-AF57267A2A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="34" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="35" r:id="rId2"/>
+    <sheet name="MARS 2026" sheetId="36" r:id="rId3"/>
+    <sheet name="AVRIL 2026" sheetId="37" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -166,6 +168,15 @@
   <si>
     <t>1 Compteurs DN 15/21 Destination Antenne Ouled dhied</t>
   </si>
+  <si>
+    <t>Mois de MARS 2026</t>
+  </si>
+  <si>
+    <t>1 Compteurs DN 15/21 Destination Antenne Seghouane</t>
+  </si>
+  <si>
+    <t>Mois de AVRIL 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -841,7 +852,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -997,6 +1008,22 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1277,6 +1304,272 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45369A9B-4B5C-45C7-BEA5-EAE54033CEF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1598B05-57E1-48DC-BCC9-A5B827D62813}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F09F360-3BFB-4277-B76B-1D5E1BE3D278}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1685,48 +1978,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -1737,36 +2030,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1778,36 +2071,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="76" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -1838,7 +2131,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="77"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -2713,149 +3006,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="60"/>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="61" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="63"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="58">
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
         <v>447</v>
       </c>
-      <c r="H43" s="64"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="49">
-        <v>0</v>
-      </c>
-      <c r="H44" s="50"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="50"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="56">
-        <v>0</v>
-      </c>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="54">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
         <v>96</v>
       </c>
-      <c r="H46" s="50"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="50"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="54">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
         <v>351</v>
       </c>
-      <c r="H47" s="50"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="50"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="47" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="49">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
         <v>321</v>
       </c>
-      <c r="H48" s="50"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="50"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="51">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
         <v>30</v>
       </c>
-      <c r="H49" s="52"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="52"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -2901,6 +3194,1277 @@
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="41">
+        <v>21</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21">
+        <v>5</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <v>11</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21">
+        <v>3</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <v>1</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21">
+        <v>5</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21">
+        <v>2</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21">
+        <v>2</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21">
+        <v>3</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="30">
+        <v>10</v>
+      </c>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21">
+        <v>1</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="30">
+        <v>10</v>
+      </c>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30">
+        <v>10</v>
+      </c>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30">
+        <v>4</v>
+      </c>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21">
+        <v>5</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21">
+        <v>1</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21">
+        <v>2</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>33</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>34</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>69</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="67"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>321</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
+        <f>L40+G45</f>
+        <v>104</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
+        <f>G43+G44-G46</f>
+        <v>217</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>214</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
+        <f>G47-G48</f>
+        <v>3</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2949,9 +4513,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
-  <dimension ref="A1:L54"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0100B2E-2FD7-43CB-9225-C8475A854F7A}">
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -2959,48 +4523,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -3011,36 +4575,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
+      <c r="A5" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -3052,36 +4616,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="76" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -3112,7 +4676,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="77"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -3121,28 +4685,28 @@
       <c r="B9" s="18">
         <v>1</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19">
-        <v>1</v>
-      </c>
-      <c r="E9" s="20"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="17">
         <f>SUM(B9:E9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="41">
-        <v>21</v>
-      </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47">
+        <v>1</v>
+      </c>
+      <c r="J9" s="47"/>
       <c r="K9" s="15">
         <f>SUM(G9:J9)</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L9" s="7">
         <f>SUM(F9+K9)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3150,53 +4714,55 @@
         <v>2</v>
       </c>
       <c r="B10" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="17">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>5</v>
-      </c>
-      <c r="G10" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="30">
+        <v>1</v>
+      </c>
       <c r="H10" s="25"/>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="15">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="B11" s="21">
+        <v>5</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="24"/>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G11" s="30"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
       <c r="K11" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3204,22 +4770,24 @@
         <v>4</v>
       </c>
       <c r="B12" s="21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
-      <c r="E12" s="23"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G12" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="30">
+        <v>2</v>
+      </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
-      <c r="J12" s="22"/>
+      <c r="J12" s="25"/>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="2"/>
@@ -3233,24 +4801,24 @@
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
-      <c r="E13" s="23"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G13" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
-      <c r="J13" s="22"/>
+      <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3260,7 +4828,7 @@
       <c r="B14" s="21"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
-      <c r="E14" s="23"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3310,7 +4878,7 @@
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
-      <c r="E16" s="23"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3332,15 +4900,13 @@
       <c r="A17" s="8">
         <v>9</v>
       </c>
-      <c r="B17" s="21">
-        <v>5</v>
-      </c>
+      <c r="B17" s="21"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="24"/>
       <c r="F17" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="30"/>
       <c r="H17" s="25"/>
@@ -3352,7 +4918,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3360,14 +4926,14 @@
         <v>10</v>
       </c>
       <c r="B18" s="21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
-      <c r="E18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="25"/>
@@ -3379,22 +4945,20 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>11</v>
       </c>
-      <c r="B19" s="21">
-        <v>2</v>
-      </c>
+      <c r="B19" s="21"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
-      <c r="E19" s="23"/>
+      <c r="E19" s="24"/>
       <c r="F19" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="30"/>
       <c r="H19" s="25"/>
@@ -3406,22 +4970,20 @@
       </c>
       <c r="L19" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>12</v>
       </c>
-      <c r="B20" s="21">
-        <v>2</v>
-      </c>
+      <c r="B20" s="21"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="24"/>
       <c r="F20" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="25"/>
@@ -3433,7 +4995,7 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3443,7 +5005,7 @@
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="23"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3468,7 +5030,7 @@
       <c r="B22" s="21"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="23"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3490,29 +5052,25 @@
       <c r="A23" s="8">
         <v>15</v>
       </c>
-      <c r="B23" s="21">
-        <v>2</v>
-      </c>
-      <c r="C23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="23"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G23" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
       <c r="H23" s="25"/>
       <c r="I23" s="25"/>
       <c r="J23" s="30"/>
       <c r="K23" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3522,57 +5080,51 @@
       <c r="B24" s="21">
         <v>3</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="23"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G24" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
       <c r="J24" s="30"/>
       <c r="K24" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>17</v>
       </c>
-      <c r="B25" s="21">
-        <v>1</v>
-      </c>
+      <c r="B25" s="21"/>
       <c r="C25" s="43"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="23"/>
+      <c r="E25" s="24"/>
       <c r="F25" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G25" s="30">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G25" s="30"/>
       <c r="H25" s="25"/>
-      <c r="I25" s="25">
-        <v>1</v>
-      </c>
+      <c r="I25" s="25"/>
       <c r="J25" s="30"/>
       <c r="K25" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3582,51 +5134,49 @@
       <c r="B26" s="21"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="23"/>
+      <c r="E26" s="24"/>
       <c r="F26" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="30">
-        <v>10</v>
-      </c>
+      <c r="G26" s="30"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="30"/>
       <c r="K26" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>19</v>
       </c>
-      <c r="B27" s="21"/>
+      <c r="B27" s="21">
+        <v>1</v>
+      </c>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="23"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="30">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G27" s="30"/>
       <c r="H27" s="25"/>
       <c r="I27" s="25"/>
       <c r="J27" s="30"/>
       <c r="K27" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3634,9 +5184,9 @@
         <v>20</v>
       </c>
       <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="23"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3659,7 +5209,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
+      <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="E29" s="24"/>
       <c r="F29" s="17">
@@ -3683,45 +5233,43 @@
       <c r="A30" s="8">
         <v>22</v>
       </c>
-      <c r="B30" s="21">
-        <v>5</v>
-      </c>
-      <c r="C30" s="22"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="23"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G30" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" s="30"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="J30" s="30"/>
       <c r="K30" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>23</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="21">
+        <v>3</v>
+      </c>
+      <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="23"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="30"/>
-      <c r="H31" s="22"/>
+      <c r="H31" s="25"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
       <c r="K31" s="15">
@@ -3730,7 +5278,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3738,9 +5286,9 @@
         <v>24</v>
       </c>
       <c r="B32" s="21"/>
-      <c r="C32" s="22"/>
+      <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="23"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3763,17 +5311,17 @@
         <v>25</v>
       </c>
       <c r="B33" s="21">
-        <v>1</v>
-      </c>
-      <c r="C33" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="C33" s="25"/>
       <c r="D33" s="25"/>
-      <c r="E33" s="23"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="30"/>
-      <c r="H33" s="22"/>
+      <c r="H33" s="25"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
       <c r="K33" s="15">
@@ -3782,7 +5330,7 @@
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3790,26 +5338,30 @@
         <v>26</v>
       </c>
       <c r="B34" s="21">
+        <v>1</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25">
         <v>2</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="23"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G34" s="30"/>
+        <v>3</v>
+      </c>
+      <c r="G34" s="30">
+        <v>1</v>
+      </c>
       <c r="H34" s="25"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
       <c r="K34" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3819,15 +5371,15 @@
       <c r="B35" s="21"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
-      <c r="E35" s="23"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G35" s="40"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
       <c r="K35" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3842,9 +5394,9 @@
         <v>28</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="22"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="25"/>
-      <c r="E36" s="23"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3852,7 +5404,7 @@
       <c r="G36" s="30"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
-      <c r="J36" s="22"/>
+      <c r="J36" s="25"/>
       <c r="K36" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3868,23 +5420,25 @@
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="25">
+        <v>1</v>
+      </c>
+      <c r="E37" s="24"/>
       <c r="F37" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="30"/>
       <c r="H37" s="25"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
       <c r="K37" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3892,16 +5446,16 @@
         <v>30</v>
       </c>
       <c r="B38" s="21"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G38" s="30"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
       <c r="J38" s="25"/>
       <c r="K38" s="15">
         <f t="shared" si="1"/>
@@ -3916,32 +5470,36 @@
       <c r="A39" s="9">
         <v>31</v>
       </c>
-      <c r="B39" s="26"/>
+      <c r="B39" s="26">
+        <v>3</v>
+      </c>
       <c r="C39" s="44"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
       <c r="F39" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="30">
+        <v>1</v>
+      </c>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
       <c r="K39" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -3949,7 +5507,7 @@
       </c>
       <c r="D40" s="46">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
@@ -3961,7 +5519,7 @@
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -3977,11 +5535,11 @@
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3999,149 +5557,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="60"/>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="61" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="63"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="58">
-        <v>321</v>
-      </c>
-      <c r="H43" s="64"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>214</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="49">
-        <v>0</v>
-      </c>
-      <c r="H44" s="50"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="50"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="56">
-        <v>0</v>
-      </c>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="54">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
-        <v>104</v>
-      </c>
-      <c r="H46" s="50"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="50"/>
+        <v>44</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="54">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
-        <v>217</v>
-      </c>
-      <c r="H47" s="50"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="50"/>
+        <v>170</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="47" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="49">
-        <v>214</v>
-      </c>
-      <c r="H48" s="50"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="50"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>169</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="51">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
-        <v>3</v>
-      </c>
-      <c r="H49" s="52"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -4166,12 +5724,7 @@
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4206,12 +5759,1227 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="A3:D3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39B34D2-8B86-4C57-A168-32452A755D66}">
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18">
+        <v>3</v>
+      </c>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>3</v>
+      </c>
+      <c r="G9" s="41"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="30"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>3</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>3</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="67"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>168</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
+        <f>L40+G45</f>
+        <v>3</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
+        <f>G43+G44-G46</f>
+        <v>165</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>165</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
+        <f>G47-G48</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="36">
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E864B58-C279-4C8A-BFCF-AF57267A2A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0904D5-EA40-4A09-9942-156D0BEA0216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="34" r:id="rId1"/>
@@ -3198,6 +3198,1277 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="41">
+        <v>21</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21">
+        <v>5</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <v>11</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21">
+        <v>3</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <v>1</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21">
+        <v>5</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21">
+        <v>2</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21">
+        <v>2</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21">
+        <v>3</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="30">
+        <v>10</v>
+      </c>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21">
+        <v>1</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="30">
+        <v>10</v>
+      </c>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30">
+        <v>10</v>
+      </c>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30">
+        <v>4</v>
+      </c>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21">
+        <v>5</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21">
+        <v>1</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21">
+        <v>2</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>33</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>34</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>69</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="67"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>321</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
+        <f>L40+G45</f>
+        <v>104</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
+        <f>G43+G44-G46</f>
+        <v>217</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>214</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
+        <f>G47-G48</f>
+        <v>3</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="I48:J48"/>
@@ -3242,9 +4513,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
-  <dimension ref="A1:L54"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0100B2E-2FD7-43CB-9225-C8475A854F7A}">
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -3321,7 +4592,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -3414,28 +4685,28 @@
       <c r="B9" s="18">
         <v>1</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19">
-        <v>1</v>
-      </c>
-      <c r="E9" s="20"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="17">
         <f>SUM(B9:E9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="41">
-        <v>21</v>
-      </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47">
+        <v>1</v>
+      </c>
+      <c r="J9" s="47"/>
       <c r="K9" s="15">
         <f>SUM(G9:J9)</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L9" s="7">
         <f>SUM(F9+K9)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3443,53 +4714,55 @@
         <v>2</v>
       </c>
       <c r="B10" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="17">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>5</v>
-      </c>
-      <c r="G10" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="30">
+        <v>1</v>
+      </c>
       <c r="H10" s="25"/>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="15">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="B11" s="21">
+        <v>5</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="24"/>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G11" s="30"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
       <c r="K11" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3497,22 +4770,24 @@
         <v>4</v>
       </c>
       <c r="B12" s="21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
-      <c r="E12" s="23"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G12" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="30">
+        <v>2</v>
+      </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
-      <c r="J12" s="22"/>
+      <c r="J12" s="25"/>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="2"/>
@@ -3526,24 +4801,24 @@
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
-      <c r="E13" s="23"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G13" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
-      <c r="J13" s="22"/>
+      <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3553,7 +4828,7 @@
       <c r="B14" s="21"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
-      <c r="E14" s="23"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3603,7 +4878,7 @@
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
-      <c r="E16" s="23"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3625,15 +4900,13 @@
       <c r="A17" s="8">
         <v>9</v>
       </c>
-      <c r="B17" s="21">
-        <v>5</v>
-      </c>
+      <c r="B17" s="21"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="24"/>
       <c r="F17" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="30"/>
       <c r="H17" s="25"/>
@@ -3645,7 +4918,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3653,14 +4926,14 @@
         <v>10</v>
       </c>
       <c r="B18" s="21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
-      <c r="E18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="25"/>
@@ -3672,22 +4945,20 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>11</v>
       </c>
-      <c r="B19" s="21">
-        <v>2</v>
-      </c>
+      <c r="B19" s="21"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
-      <c r="E19" s="23"/>
+      <c r="E19" s="24"/>
       <c r="F19" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="30"/>
       <c r="H19" s="25"/>
@@ -3699,22 +4970,20 @@
       </c>
       <c r="L19" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>12</v>
       </c>
-      <c r="B20" s="21">
-        <v>2</v>
-      </c>
+      <c r="B20" s="21"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="24"/>
       <c r="F20" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="25"/>
@@ -3726,7 +4995,7 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3736,7 +5005,7 @@
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="23"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3761,7 +5030,7 @@
       <c r="B22" s="21"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="23"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3783,29 +5052,25 @@
       <c r="A23" s="8">
         <v>15</v>
       </c>
-      <c r="B23" s="21">
-        <v>2</v>
-      </c>
-      <c r="C23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="23"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G23" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
       <c r="H23" s="25"/>
       <c r="I23" s="25"/>
       <c r="J23" s="30"/>
       <c r="K23" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3815,57 +5080,51 @@
       <c r="B24" s="21">
         <v>3</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="23"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G24" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
       <c r="J24" s="30"/>
       <c r="K24" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>17</v>
       </c>
-      <c r="B25" s="21">
-        <v>1</v>
-      </c>
+      <c r="B25" s="21"/>
       <c r="C25" s="43"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="23"/>
+      <c r="E25" s="24"/>
       <c r="F25" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G25" s="30">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G25" s="30"/>
       <c r="H25" s="25"/>
-      <c r="I25" s="25">
-        <v>1</v>
-      </c>
+      <c r="I25" s="25"/>
       <c r="J25" s="30"/>
       <c r="K25" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3875,51 +5134,49 @@
       <c r="B26" s="21"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="23"/>
+      <c r="E26" s="24"/>
       <c r="F26" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="30">
-        <v>10</v>
-      </c>
+      <c r="G26" s="30"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="30"/>
       <c r="K26" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>19</v>
       </c>
-      <c r="B27" s="21"/>
+      <c r="B27" s="21">
+        <v>1</v>
+      </c>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="23"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="30">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G27" s="30"/>
       <c r="H27" s="25"/>
       <c r="I27" s="25"/>
       <c r="J27" s="30"/>
       <c r="K27" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3927,9 +5184,9 @@
         <v>20</v>
       </c>
       <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="23"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3952,7 +5209,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
+      <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="E29" s="24"/>
       <c r="F29" s="17">
@@ -3976,45 +5233,43 @@
       <c r="A30" s="8">
         <v>22</v>
       </c>
-      <c r="B30" s="21">
-        <v>5</v>
-      </c>
-      <c r="C30" s="22"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="23"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G30" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" s="30"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="J30" s="30"/>
       <c r="K30" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>23</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="21">
+        <v>3</v>
+      </c>
+      <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="23"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="30"/>
-      <c r="H31" s="22"/>
+      <c r="H31" s="25"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
       <c r="K31" s="15">
@@ -4023,7 +5278,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4031,9 +5286,9 @@
         <v>24</v>
       </c>
       <c r="B32" s="21"/>
-      <c r="C32" s="22"/>
+      <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="23"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4056,17 +5311,17 @@
         <v>25</v>
       </c>
       <c r="B33" s="21">
-        <v>1</v>
-      </c>
-      <c r="C33" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="C33" s="25"/>
       <c r="D33" s="25"/>
-      <c r="E33" s="23"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="30"/>
-      <c r="H33" s="22"/>
+      <c r="H33" s="25"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
       <c r="K33" s="15">
@@ -4075,7 +5330,7 @@
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4083,26 +5338,30 @@
         <v>26</v>
       </c>
       <c r="B34" s="21">
+        <v>1</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25">
         <v>2</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="23"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G34" s="30"/>
+        <v>3</v>
+      </c>
+      <c r="G34" s="30">
+        <v>1</v>
+      </c>
       <c r="H34" s="25"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
       <c r="K34" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4112,15 +5371,15 @@
       <c r="B35" s="21"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
-      <c r="E35" s="23"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G35" s="40"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
       <c r="K35" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4135,9 +5394,9 @@
         <v>28</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="22"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="25"/>
-      <c r="E36" s="23"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4145,7 +5404,7 @@
       <c r="G36" s="30"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
-      <c r="J36" s="22"/>
+      <c r="J36" s="25"/>
       <c r="K36" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4161,23 +5420,25 @@
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="25">
+        <v>1</v>
+      </c>
+      <c r="E37" s="24"/>
       <c r="F37" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="30"/>
       <c r="H37" s="25"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
       <c r="K37" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4185,16 +5446,16 @@
         <v>30</v>
       </c>
       <c r="B38" s="21"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G38" s="30"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
       <c r="J38" s="25"/>
       <c r="K38" s="15">
         <f t="shared" si="1"/>
@@ -4209,32 +5470,36 @@
       <c r="A39" s="9">
         <v>31</v>
       </c>
-      <c r="B39" s="26"/>
+      <c r="B39" s="26">
+        <v>3</v>
+      </c>
       <c r="C39" s="44"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
       <c r="F39" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="30">
+        <v>1</v>
+      </c>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
       <c r="K39" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -4242,7 +5507,7 @@
       </c>
       <c r="D40" s="46">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
@@ -4254,7 +5519,7 @@
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -4270,11 +5535,11 @@
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4319,7 +5584,7 @@
       <c r="E43" s="52"/>
       <c r="F43" s="52"/>
       <c r="G43" s="62">
-        <v>321</v>
+        <v>214</v>
       </c>
       <c r="H43" s="68"/>
       <c r="I43" s="69"/>
@@ -4374,7 +5639,7 @@
       <c r="F46" s="52"/>
       <c r="G46" s="58">
         <f>L40+G45</f>
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="H46" s="54"/>
       <c r="I46" s="53"/>
@@ -4393,7 +5658,7 @@
       <c r="F47" s="52"/>
       <c r="G47" s="58">
         <f>G43+G44-G46</f>
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="H47" s="54"/>
       <c r="I47" s="53"/>
@@ -4411,7 +5676,7 @@
       <c r="E48" s="52"/>
       <c r="F48" s="52"/>
       <c r="G48" s="53">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="H48" s="54"/>
       <c r="I48" s="53"/>
@@ -4430,7 +5695,7 @@
       <c r="F49" s="52"/>
       <c r="G49" s="55">
         <f>G47-G48</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49" s="56"/>
       <c r="I49" s="57"/>
@@ -4459,12 +5724,7 @@
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4513,9 +5773,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0100B2E-2FD7-43CB-9225-C8475A854F7A}">
-  <dimension ref="A1:L53"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39B34D2-8B86-4C57-A168-32452A755D66}">
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -4592,7 +5852,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -4683,26 +5943,22 @@
         <v>1</v>
       </c>
       <c r="B9" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="48"/>
       <c r="D9" s="48"/>
       <c r="E9" s="49"/>
       <c r="F9" s="17">
         <f>SUM(B9:E9)</f>
-        <v>1</v>
-      </c>
-      <c r="G9" s="41">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G9" s="41"/>
       <c r="H9" s="47"/>
-      <c r="I9" s="47">
-        <v>1</v>
-      </c>
+      <c r="I9" s="47"/>
       <c r="J9" s="47"/>
       <c r="K9" s="15">
         <f>SUM(G9:J9)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="7">
         <f>SUM(F9+K9)</f>
@@ -4713,44 +5969,38 @@
       <c r="A10" s="8">
         <v>2</v>
       </c>
-      <c r="B10" s="21">
-        <v>1</v>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="24"/>
       <c r="F10" s="17">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="15">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="B11" s="21">
-        <v>5</v>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="24"/>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="25"/>
@@ -4762,36 +6012,32 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>4</v>
       </c>
-      <c r="B12" s="21">
-        <v>1</v>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="24"/>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G12" s="30">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="J12" s="25"/>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4806,19 +6052,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="30">
-        <v>2</v>
-      </c>
+      <c r="G13" s="30"/>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
       <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4925,15 +6169,13 @@
       <c r="A18" s="8">
         <v>10</v>
       </c>
-      <c r="B18" s="21">
-        <v>10</v>
-      </c>
+      <c r="B18" s="21"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
       <c r="E18" s="24"/>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="25"/>
@@ -4945,7 +6187,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5077,29 +6319,25 @@
       <c r="A24" s="8">
         <v>16</v>
       </c>
-      <c r="B24" s="21">
-        <v>3</v>
-      </c>
+      <c r="B24" s="21"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G24" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G24" s="30"/>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
       <c r="J24" s="30"/>
       <c r="K24" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5156,15 +6394,13 @@
       <c r="A27" s="8">
         <v>19</v>
       </c>
-      <c r="B27" s="21">
-        <v>1</v>
-      </c>
+      <c r="B27" s="21"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
       <c r="E27" s="24"/>
       <c r="F27" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="30"/>
       <c r="H27" s="25"/>
@@ -5176,7 +6412,7 @@
       </c>
       <c r="L27" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5258,15 +6494,13 @@
       <c r="A31" s="8">
         <v>23</v>
       </c>
-      <c r="B31" s="21">
-        <v>3</v>
-      </c>
+      <c r="B31" s="21"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="25"/>
@@ -5278,7 +6512,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5310,15 +6544,13 @@
       <c r="A33" s="8">
         <v>25</v>
       </c>
-      <c r="B33" s="21">
-        <v>2</v>
-      </c>
+      <c r="B33" s="21"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="E33" s="24"/>
       <c r="F33" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" s="30"/>
       <c r="H33" s="25"/>
@@ -5330,38 +6562,32 @@
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>26</v>
       </c>
-      <c r="B34" s="21">
-        <v>1</v>
-      </c>
+      <c r="B34" s="21"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="25">
-        <v>2</v>
-      </c>
+      <c r="D34" s="25"/>
       <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G34" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G34" s="30"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
       <c r="K34" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5420,13 +6646,11 @@
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="25">
-        <v>1</v>
-      </c>
+      <c r="D37" s="25"/>
       <c r="E37" s="24"/>
       <c r="F37" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="30"/>
       <c r="H37" s="25"/>
@@ -5438,7 +6662,7 @@
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5470,36 +6694,32 @@
       <c r="A39" s="9">
         <v>31</v>
       </c>
-      <c r="B39" s="26">
-        <v>3</v>
-      </c>
+      <c r="B39" s="26"/>
       <c r="C39" s="44"/>
       <c r="D39" s="44"/>
       <c r="E39" s="50"/>
       <c r="F39" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G39" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
       <c r="H39" s="25"/>
       <c r="I39" s="25"/>
       <c r="J39" s="25"/>
       <c r="K39" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -5507,7 +6727,7 @@
       </c>
       <c r="D40" s="46">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
@@ -5515,11 +6735,11 @@
       </c>
       <c r="F40" s="45">
         <f>SUM(F9:F39)</f>
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -5527,7 +6747,7 @@
       </c>
       <c r="I40" s="16">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="16">
         <f t="shared" si="4"/>
@@ -5535,11 +6755,11 @@
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5584,7 +6804,7 @@
       <c r="E43" s="52"/>
       <c r="F43" s="52"/>
       <c r="G43" s="62">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="H43" s="68"/>
       <c r="I43" s="69"/>
@@ -5639,7 +6859,7 @@
       <c r="F46" s="52"/>
       <c r="G46" s="58">
         <f>L40+G45</f>
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H46" s="54"/>
       <c r="I46" s="53"/>
@@ -5658,7 +6878,7 @@
       <c r="F47" s="52"/>
       <c r="G47" s="58">
         <f>G43+G44-G46</f>
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H47" s="54"/>
       <c r="I47" s="53"/>
@@ -5676,7 +6896,7 @@
       <c r="E48" s="52"/>
       <c r="F48" s="52"/>
       <c r="G48" s="53">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H48" s="54"/>
       <c r="I48" s="53"/>
@@ -5722,11 +6942,6 @@
       <c r="L50" s="1"/>
     </row>
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>38</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B48:F48"/>
@@ -5771,1219 +6986,4 @@
   <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39B34D2-8B86-4C57-A168-32452A755D66}">
-  <dimension ref="A1:L51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="12" width="8.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="84" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-    </row>
-    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="81"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>1</v>
-      </c>
-      <c r="B9" s="18">
-        <v>3</v>
-      </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="17">
-        <f>SUM(B9:E9)</f>
-        <v>3</v>
-      </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="15">
-        <f>SUM(G9:J9)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="7">
-        <f>SUM(F9+K9)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
-        <v>2</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="17">
-        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="15">
-        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="7">
-        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>4</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>5</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>6</v>
-      </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="30"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>7</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>8</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>9</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>10</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>11</v>
-      </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="30"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>12</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>13</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>14</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="30"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>15</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
-        <v>16</v>
-      </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
-        <v>17</v>
-      </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>18</v>
-      </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>19</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="30"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
-        <v>20</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>21</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="30"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>22</v>
-      </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
-        <v>23</v>
-      </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="30"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>24</v>
-      </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="30"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
-        <v>25</v>
-      </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
-        <v>26</v>
-      </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="30"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
-        <v>27</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="40"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
-        <v>28</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="30"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
-        <v>29</v>
-      </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="30"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
-        <v>30</v>
-      </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="30"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9">
-        <v>31</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L39" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="46">
-        <f>SUM(B9:B39)</f>
-        <v>3</v>
-      </c>
-      <c r="C40" s="46">
-        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="46">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="46">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="45">
-        <f>SUM(F9:F39)</f>
-        <v>3</v>
-      </c>
-      <c r="G40" s="16">
-        <f>SUM(G9:G39)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="16">
-        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="16">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="16">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="16">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="16">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="13"/>
-    </row>
-    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="67"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="13"/>
-    </row>
-    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
-      <c r="B43" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="62">
-        <v>168</v>
-      </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="13"/>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53">
-        <v>0</v>
-      </c>
-      <c r="H44" s="54"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="54"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="13"/>
-    </row>
-    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="60">
-        <v>0</v>
-      </c>
-      <c r="H45" s="61"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="63"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="13"/>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="14"/>
-      <c r="B46" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="58">
-        <f>L40+G45</f>
-        <v>3</v>
-      </c>
-      <c r="H46" s="54"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="54"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="13"/>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="58">
-        <f>G43+G44-G46</f>
-        <v>165</v>
-      </c>
-      <c r="H47" s="54"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53">
-        <v>165</v>
-      </c>
-      <c r="H48" s="54"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="54"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="55">
-        <f>G47-G48</f>
-        <v>0</v>
-      </c>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="56"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B50" s="32"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="J50" s="38"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="1"/>
-    </row>
-    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="G2:L2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0904D5-EA40-4A09-9942-156D0BEA0216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B820A61-6E0D-48CE-868B-6556B7285881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="43">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -177,6 +177,15 @@
   <si>
     <t>Mois de AVRIL 2026</t>
   </si>
+  <si>
+    <t>3 Compteurs DN 15/21 Destination Antenne Oueld dhied</t>
+  </si>
+  <si>
+    <t>6 Compteurs DN 15/21 Destination Antenne Tlathet-douairs</t>
+  </si>
+  <si>
+    <t>1 Compteurs DN 30 Destination Agence Beni Slimane</t>
+  </si>
 </sst>
 </file>
 
@@ -1025,28 +1034,82 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="2" borderId="41" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1060,74 +1123,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="2" borderId="41" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1978,48 +1987,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
+      <c r="G1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -2030,36 +2039,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -2071,36 +2080,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="80" t="s">
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -2131,7 +2140,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="81"/>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -3006,149 +3015,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65" t="s">
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66" t="s">
+      <c r="H42" s="67"/>
+      <c r="I42" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="67"/>
+      <c r="J42" s="68"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="62">
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71">
         <v>447</v>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53">
-        <v>0</v>
-      </c>
-      <c r="H44" s="54"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="54"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="75">
+        <v>0</v>
+      </c>
+      <c r="H44" s="76"/>
+      <c r="I44" s="75"/>
+      <c r="J44" s="76"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="60">
-        <v>0</v>
-      </c>
-      <c r="H45" s="61"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="63"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="78">
+        <v>0</v>
+      </c>
+      <c r="H45" s="79"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="80"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="58">
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="81">
         <f>L40+G45</f>
         <v>96</v>
       </c>
-      <c r="H46" s="54"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="54"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="75"/>
+      <c r="J46" s="76"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="58">
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="81">
         <f>G43+G44-G46</f>
         <v>351</v>
       </c>
-      <c r="H47" s="54"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="54"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53">
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="75">
         <v>321</v>
       </c>
-      <c r="H48" s="54"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="54"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="55">
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="82">
         <f>G47-G48</f>
         <v>30</v>
       </c>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="56"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="83"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -3252,48 +3261,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
+      <c r="G1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -3304,36 +3313,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -3345,36 +3354,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="80" t="s">
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -3405,7 +3414,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="81"/>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -4292,149 +4301,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65" t="s">
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66" t="s">
+      <c r="H42" s="67"/>
+      <c r="I42" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="67"/>
+      <c r="J42" s="68"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="62">
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71">
         <v>321</v>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53">
-        <v>0</v>
-      </c>
-      <c r="H44" s="54"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="54"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="75">
+        <v>0</v>
+      </c>
+      <c r="H44" s="76"/>
+      <c r="I44" s="75"/>
+      <c r="J44" s="76"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="60">
-        <v>0</v>
-      </c>
-      <c r="H45" s="61"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="63"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="78">
+        <v>0</v>
+      </c>
+      <c r="H45" s="79"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="80"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="58">
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="81">
         <f>L40+G45</f>
         <v>104</v>
       </c>
-      <c r="H46" s="54"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="54"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="75"/>
+      <c r="J46" s="76"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="58">
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="81">
         <f>G43+G44-G46</f>
         <v>217</v>
       </c>
-      <c r="H47" s="54"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="54"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53">
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="75">
         <v>214</v>
       </c>
-      <c r="H48" s="54"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="54"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="55">
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="82">
         <f>G47-G48</f>
         <v>3</v>
       </c>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="56"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="83"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -4523,48 +4532,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
+      <c r="G1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -4575,36 +4584,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -4616,36 +4625,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="80" t="s">
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -4676,7 +4685,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="81"/>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -5557,149 +5566,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65" t="s">
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66" t="s">
+      <c r="H42" s="67"/>
+      <c r="I42" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="67"/>
+      <c r="J42" s="68"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="62">
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71">
         <v>214</v>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53">
-        <v>0</v>
-      </c>
-      <c r="H44" s="54"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="54"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="75">
+        <v>0</v>
+      </c>
+      <c r="H44" s="76"/>
+      <c r="I44" s="75"/>
+      <c r="J44" s="76"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="60">
-        <v>0</v>
-      </c>
-      <c r="H45" s="61"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="63"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="78">
+        <v>0</v>
+      </c>
+      <c r="H45" s="79"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="80"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="58">
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="81">
         <f>L40+G45</f>
         <v>44</v>
       </c>
-      <c r="H46" s="54"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="54"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="75"/>
+      <c r="J46" s="76"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="58">
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="81">
         <f>G43+G44-G46</f>
         <v>170</v>
       </c>
-      <c r="H47" s="54"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="54"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53">
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="75">
         <v>169</v>
       </c>
-      <c r="H48" s="54"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="54"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="55">
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="82">
         <f>G47-G48</f>
         <v>1</v>
       </c>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="56"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="83"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -5775,7 +5784,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39B34D2-8B86-4C57-A168-32452A755D66}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -5783,48 +5792,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
+      <c r="G1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -5835,36 +5844,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -5876,36 +5885,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="80" t="s">
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -5936,7 +5945,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="81"/>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -6044,25 +6053,31 @@
       <c r="A13" s="8">
         <v>5</v>
       </c>
-      <c r="B13" s="21"/>
+      <c r="B13" s="21">
+        <v>2</v>
+      </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="24"/>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="30"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="30">
+        <v>3</v>
+      </c>
       <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="25">
+        <v>1</v>
+      </c>
       <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6094,25 +6109,29 @@
       <c r="A15" s="8">
         <v>7</v>
       </c>
-      <c r="B15" s="21"/>
+      <c r="B15" s="21">
+        <v>3</v>
+      </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="30"/>
+        <v>3</v>
+      </c>
+      <c r="G15" s="30">
+        <v>7</v>
+      </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
       <c r="J15" s="30"/>
       <c r="K15" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6127,17 +6146,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="30">
+        <v>12</v>
+      </c>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="J16" s="30"/>
       <c r="K16" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6219,13 +6240,17 @@
       <c r="A20" s="8">
         <v>12</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
+      <c r="D20" s="25">
+        <v>2</v>
+      </c>
       <c r="E20" s="24"/>
       <c r="F20" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="25"/>
@@ -6237,7 +6262,7 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6269,13 +6294,15 @@
       <c r="A22" s="8">
         <v>14</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="21">
+        <v>1</v>
+      </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
       <c r="E22" s="24"/>
       <c r="F22" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="25"/>
@@ -6287,45 +6314,53 @@
       </c>
       <c r="L22" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>15</v>
       </c>
-      <c r="B23" s="21"/>
+      <c r="B23" s="21">
+        <v>1</v>
+      </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="24"/>
       <c r="F23" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="25"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25">
+        <v>1</v>
+      </c>
       <c r="I23" s="25"/>
       <c r="J23" s="30"/>
       <c r="K23" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>16</v>
       </c>
-      <c r="B24" s="21"/>
+      <c r="B24" s="21">
+        <v>2</v>
+      </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="30"/>
       <c r="H24" s="25"/>
@@ -6337,7 +6372,7 @@
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6379,15 +6414,17 @@
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="I26" s="25">
+        <v>1</v>
+      </c>
       <c r="J26" s="30"/>
       <c r="K26" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6452,30 +6489,34 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="30"/>
+      <c r="G29" s="30">
+        <v>9</v>
+      </c>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="J29" s="30"/>
       <c r="K29" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>22</v>
       </c>
-      <c r="B30" s="21"/>
+      <c r="B30" s="21">
+        <v>4</v>
+      </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="E30" s="24"/>
       <c r="F30" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G30" s="30"/>
       <c r="H30" s="25"/>
@@ -6487,20 +6528,22 @@
       </c>
       <c r="L30" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>23</v>
       </c>
-      <c r="B31" s="21"/>
+      <c r="B31" s="21">
+        <v>1</v>
+      </c>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="25"/>
@@ -6512,7 +6555,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6552,30 +6595,34 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G33" s="30"/>
+      <c r="G33" s="30">
+        <v>10</v>
+      </c>
       <c r="H33" s="25"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
       <c r="K33" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>26</v>
       </c>
-      <c r="B34" s="21"/>
+      <c r="B34" s="21">
+        <v>4</v>
+      </c>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G34" s="30"/>
       <c r="H34" s="25"/>
@@ -6587,45 +6634,51 @@
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>27</v>
       </c>
-      <c r="B35" s="21"/>
+      <c r="B35" s="21">
+        <v>1</v>
+      </c>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="E35" s="24"/>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="40"/>
-      <c r="H35" s="25"/>
+      <c r="H35" s="25">
+        <v>1</v>
+      </c>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
       <c r="K35" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>28</v>
       </c>
-      <c r="B36" s="21"/>
+      <c r="B36" s="21">
+        <v>3</v>
+      </c>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="E36" s="24"/>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="30"/>
       <c r="H36" s="25"/>
@@ -6637,7 +6690,7 @@
       </c>
       <c r="L36" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6652,30 +6705,34 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G37" s="30"/>
+      <c r="G37" s="30">
+        <v>3</v>
+      </c>
       <c r="H37" s="25"/>
       <c r="I37" s="25"/>
       <c r="J37" s="25"/>
       <c r="K37" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>30</v>
       </c>
-      <c r="B38" s="21"/>
+      <c r="B38" s="21">
+        <v>2</v>
+      </c>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="24"/>
       <c r="F38" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="30"/>
       <c r="H38" s="25"/>
@@ -6687,7 +6744,7 @@
       </c>
       <c r="L38" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6719,7 +6776,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -6727,7 +6784,7 @@
       </c>
       <c r="D40" s="46">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
@@ -6735,19 +6792,19 @@
       </c>
       <c r="F40" s="45">
         <f>SUM(F9:F39)</f>
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" s="16">
         <f t="shared" si="4"/>
@@ -6755,11 +6812,11 @@
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6777,149 +6834,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65" t="s">
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66" t="s">
+      <c r="H42" s="67"/>
+      <c r="I42" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="67"/>
+      <c r="J42" s="68"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="62">
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71">
         <v>169</v>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53">
-        <v>0</v>
-      </c>
-      <c r="H44" s="54"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="54"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="75">
+        <v>1</v>
+      </c>
+      <c r="H44" s="76"/>
+      <c r="I44" s="75"/>
+      <c r="J44" s="76"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="60">
-        <v>0</v>
-      </c>
-      <c r="H45" s="61"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="63"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="78">
+        <v>0</v>
+      </c>
+      <c r="H45" s="79"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="80"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="58">
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="81">
         <f>L40+G45</f>
-        <v>3</v>
-      </c>
-      <c r="H46" s="54"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="54"/>
+        <v>80</v>
+      </c>
+      <c r="H46" s="76"/>
+      <c r="I46" s="75"/>
+      <c r="J46" s="76"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="58">
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="81">
         <f>G43+G44-G46</f>
-        <v>166</v>
-      </c>
-      <c r="H47" s="54"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="54"/>
+        <v>90</v>
+      </c>
+      <c r="H47" s="76"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53">
-        <v>165</v>
-      </c>
-      <c r="H48" s="54"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="54"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="75">
+        <v>78</v>
+      </c>
+      <c r="H48" s="76"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="55">
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="82">
         <f>G47-G48</f>
-        <v>1</v>
-      </c>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="56"/>
+        <v>12</v>
+      </c>
+      <c r="H49" s="83"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="83"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -6942,6 +6999,26 @@
       <c r="L50" s="1"/>
     </row>
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B48:F48"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B820A61-6E0D-48CE-868B-6556B7285881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5E97EB-A93F-4497-871D-BA515F60CEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="34" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="35" r:id="rId2"/>
     <sheet name="MARS 2026" sheetId="36" r:id="rId3"/>
     <sheet name="AVRIL 2026" sheetId="37" r:id="rId4"/>
+    <sheet name="MAI 2026" sheetId="38" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="49">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -185,6 +186,24 @@
   </si>
   <si>
     <t>1 Compteurs DN 30 Destination Agence Beni Slimane</t>
+  </si>
+  <si>
+    <t>Mois de MAI 2026</t>
+  </si>
+  <si>
+    <t>01 Compteurs DN 15/21 Destination Seghouane</t>
+  </si>
+  <si>
+    <t>01 Compteurs DN 100 Destination Seghouane</t>
+  </si>
+  <si>
+    <t>06 Compteurs DN 15/21 Destination Tlathet Douairs</t>
+  </si>
+  <si>
+    <t>03 Compteurs DN 15/21 Destination Zoubiria</t>
+  </si>
+  <si>
+    <t>06 Compteurs : 2 (DN 15/21) , 1 (DN 100) ,1 (DN 80), 1 (DN 65) , 1 (DN 50)  Destination Antenne Robea</t>
   </si>
 </sst>
 </file>
@@ -1691,6 +1710,139 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0307A68D-7CC6-45A0-8CF6-B93CA6C05DBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3207,6 +3359,1277 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="58"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="64"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="41">
+        <v>21</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21">
+        <v>5</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <v>11</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21">
+        <v>3</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <v>1</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21">
+        <v>5</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21">
+        <v>2</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21">
+        <v>2</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21">
+        <v>3</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="30">
+        <v>10</v>
+      </c>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21">
+        <v>1</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="30">
+        <v>10</v>
+      </c>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30">
+        <v>10</v>
+      </c>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30">
+        <v>4</v>
+      </c>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21">
+        <v>5</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21">
+        <v>1</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21">
+        <v>2</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>33</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>34</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>69</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="68"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71">
+        <v>321</v>
+      </c>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="75">
+        <v>0</v>
+      </c>
+      <c r="H44" s="76"/>
+      <c r="I44" s="75"/>
+      <c r="J44" s="76"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="78">
+        <v>0</v>
+      </c>
+      <c r="H45" s="79"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="81">
+        <f>L40+G45</f>
+        <v>104</v>
+      </c>
+      <c r="H46" s="76"/>
+      <c r="I46" s="75"/>
+      <c r="J46" s="76"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="81">
+        <f>G43+G44-G46</f>
+        <v>217</v>
+      </c>
+      <c r="H47" s="76"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="75">
+        <v>214</v>
+      </c>
+      <c r="H48" s="76"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="82">
+        <f>G47-G48</f>
+        <v>3</v>
+      </c>
+      <c r="H49" s="83"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="83"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G1:L1"/>
@@ -3251,9 +4674,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A789F73-A3BB-4886-8995-5105552B61B3}">
-  <dimension ref="A1:L54"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0100B2E-2FD7-43CB-9225-C8475A854F7A}">
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -3330,7 +4753,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55"/>
@@ -3423,28 +4846,28 @@
       <c r="B9" s="18">
         <v>1</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19">
-        <v>1</v>
-      </c>
-      <c r="E9" s="20"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="17">
         <f>SUM(B9:E9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="41">
-        <v>21</v>
-      </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47">
+        <v>1</v>
+      </c>
+      <c r="J9" s="47"/>
       <c r="K9" s="15">
         <f>SUM(G9:J9)</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L9" s="7">
         <f>SUM(F9+K9)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3452,53 +4875,55 @@
         <v>2</v>
       </c>
       <c r="B10" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="17">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>5</v>
-      </c>
-      <c r="G10" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="30">
+        <v>1</v>
+      </c>
       <c r="H10" s="25"/>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="15">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="B11" s="21">
+        <v>5</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="24"/>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G11" s="30"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
       <c r="K11" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3506,22 +4931,24 @@
         <v>4</v>
       </c>
       <c r="B12" s="21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
-      <c r="E12" s="23"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G12" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="30">
+        <v>2</v>
+      </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
-      <c r="J12" s="22"/>
+      <c r="J12" s="25"/>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="2"/>
@@ -3535,24 +4962,24 @@
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
-      <c r="E13" s="23"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G13" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
-      <c r="J13" s="22"/>
+      <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3562,7 +4989,7 @@
       <c r="B14" s="21"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
-      <c r="E14" s="23"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3612,7 +5039,7 @@
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
-      <c r="E16" s="23"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3634,15 +5061,13 @@
       <c r="A17" s="8">
         <v>9</v>
       </c>
-      <c r="B17" s="21">
-        <v>5</v>
-      </c>
+      <c r="B17" s="21"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="24"/>
       <c r="F17" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="30"/>
       <c r="H17" s="25"/>
@@ -3654,7 +5079,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3662,14 +5087,14 @@
         <v>10</v>
       </c>
       <c r="B18" s="21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
-      <c r="E18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="25"/>
@@ -3681,22 +5106,20 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>11</v>
       </c>
-      <c r="B19" s="21">
-        <v>2</v>
-      </c>
+      <c r="B19" s="21"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
-      <c r="E19" s="23"/>
+      <c r="E19" s="24"/>
       <c r="F19" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="30"/>
       <c r="H19" s="25"/>
@@ -3708,22 +5131,20 @@
       </c>
       <c r="L19" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>12</v>
       </c>
-      <c r="B20" s="21">
-        <v>2</v>
-      </c>
+      <c r="B20" s="21"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="24"/>
       <c r="F20" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="25"/>
@@ -3735,7 +5156,7 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3745,7 +5166,7 @@
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="23"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3770,7 +5191,7 @@
       <c r="B22" s="21"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="23"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3792,29 +5213,25 @@
       <c r="A23" s="8">
         <v>15</v>
       </c>
-      <c r="B23" s="21">
-        <v>2</v>
-      </c>
-      <c r="C23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="23"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G23" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
       <c r="H23" s="25"/>
       <c r="I23" s="25"/>
       <c r="J23" s="30"/>
       <c r="K23" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3824,57 +5241,51 @@
       <c r="B24" s="21">
         <v>3</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="23"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G24" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
       <c r="J24" s="30"/>
       <c r="K24" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>17</v>
       </c>
-      <c r="B25" s="21">
-        <v>1</v>
-      </c>
+      <c r="B25" s="21"/>
       <c r="C25" s="43"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="23"/>
+      <c r="E25" s="24"/>
       <c r="F25" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G25" s="30">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G25" s="30"/>
       <c r="H25" s="25"/>
-      <c r="I25" s="25">
-        <v>1</v>
-      </c>
+      <c r="I25" s="25"/>
       <c r="J25" s="30"/>
       <c r="K25" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3884,51 +5295,49 @@
       <c r="B26" s="21"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="23"/>
+      <c r="E26" s="24"/>
       <c r="F26" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="30">
-        <v>10</v>
-      </c>
+      <c r="G26" s="30"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="30"/>
       <c r="K26" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>19</v>
       </c>
-      <c r="B27" s="21"/>
+      <c r="B27" s="21">
+        <v>1</v>
+      </c>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="23"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="30">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G27" s="30"/>
       <c r="H27" s="25"/>
       <c r="I27" s="25"/>
       <c r="J27" s="30"/>
       <c r="K27" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3936,9 +5345,9 @@
         <v>20</v>
       </c>
       <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="23"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3961,7 +5370,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
+      <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="E29" s="24"/>
       <c r="F29" s="17">
@@ -3985,45 +5394,43 @@
       <c r="A30" s="8">
         <v>22</v>
       </c>
-      <c r="B30" s="21">
-        <v>5</v>
-      </c>
-      <c r="C30" s="22"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="23"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G30" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" s="30"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="J30" s="30"/>
       <c r="K30" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>23</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="21">
+        <v>3</v>
+      </c>
+      <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="23"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="30"/>
-      <c r="H31" s="22"/>
+      <c r="H31" s="25"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
       <c r="K31" s="15">
@@ -4032,7 +5439,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4040,9 +5447,9 @@
         <v>24</v>
       </c>
       <c r="B32" s="21"/>
-      <c r="C32" s="22"/>
+      <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="23"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4065,17 +5472,17 @@
         <v>25</v>
       </c>
       <c r="B33" s="21">
-        <v>1</v>
-      </c>
-      <c r="C33" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="C33" s="25"/>
       <c r="D33" s="25"/>
-      <c r="E33" s="23"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="30"/>
-      <c r="H33" s="22"/>
+      <c r="H33" s="25"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
       <c r="K33" s="15">
@@ -4084,7 +5491,7 @@
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4092,26 +5499,30 @@
         <v>26</v>
       </c>
       <c r="B34" s="21">
+        <v>1</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25">
         <v>2</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="23"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G34" s="30"/>
+        <v>3</v>
+      </c>
+      <c r="G34" s="30">
+        <v>1</v>
+      </c>
       <c r="H34" s="25"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
       <c r="K34" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4121,15 +5532,15 @@
       <c r="B35" s="21"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
-      <c r="E35" s="23"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G35" s="40"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
       <c r="K35" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4144,9 +5555,9 @@
         <v>28</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="22"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="25"/>
-      <c r="E36" s="23"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4154,7 +5565,7 @@
       <c r="G36" s="30"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
-      <c r="J36" s="22"/>
+      <c r="J36" s="25"/>
       <c r="K36" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4170,23 +5581,25 @@
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="25">
+        <v>1</v>
+      </c>
+      <c r="E37" s="24"/>
       <c r="F37" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="30"/>
       <c r="H37" s="25"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
       <c r="K37" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4194,16 +5607,16 @@
         <v>30</v>
       </c>
       <c r="B38" s="21"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G38" s="30"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
       <c r="J38" s="25"/>
       <c r="K38" s="15">
         <f t="shared" si="1"/>
@@ -4218,32 +5631,36 @@
       <c r="A39" s="9">
         <v>31</v>
       </c>
-      <c r="B39" s="26"/>
+      <c r="B39" s="26">
+        <v>3</v>
+      </c>
       <c r="C39" s="44"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
       <c r="F39" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="30">
+        <v>1</v>
+      </c>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
       <c r="K39" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -4251,7 +5668,7 @@
       </c>
       <c r="D40" s="46">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
@@ -4263,7 +5680,7 @@
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -4279,11 +5696,11 @@
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4328,7 +5745,7 @@
       <c r="E43" s="70"/>
       <c r="F43" s="70"/>
       <c r="G43" s="71">
-        <v>321</v>
+        <v>214</v>
       </c>
       <c r="H43" s="72"/>
       <c r="I43" s="73"/>
@@ -4383,7 +5800,7 @@
       <c r="F46" s="70"/>
       <c r="G46" s="81">
         <f>L40+G45</f>
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="H46" s="76"/>
       <c r="I46" s="75"/>
@@ -4402,7 +5819,7 @@
       <c r="F47" s="70"/>
       <c r="G47" s="81">
         <f>G43+G44-G46</f>
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="H47" s="76"/>
       <c r="I47" s="75"/>
@@ -4420,7 +5837,7 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="75">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="H48" s="76"/>
       <c r="I48" s="75"/>
@@ -4439,7 +5856,7 @@
       <c r="F49" s="70"/>
       <c r="G49" s="82">
         <f>G47-G48</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49" s="83"/>
       <c r="I49" s="84"/>
@@ -4468,12 +5885,7 @@
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4522,9 +5934,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0100B2E-2FD7-43CB-9225-C8475A854F7A}">
-  <dimension ref="A1:L53"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39B34D2-8B86-4C57-A168-32452A755D66}">
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -4601,7 +6013,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55"/>
@@ -4692,26 +6104,22 @@
         <v>1</v>
       </c>
       <c r="B9" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="48"/>
       <c r="D9" s="48"/>
       <c r="E9" s="49"/>
       <c r="F9" s="17">
         <f>SUM(B9:E9)</f>
-        <v>1</v>
-      </c>
-      <c r="G9" s="41">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G9" s="41"/>
       <c r="H9" s="47"/>
-      <c r="I9" s="47">
-        <v>1</v>
-      </c>
+      <c r="I9" s="47"/>
       <c r="J9" s="47"/>
       <c r="K9" s="15">
         <f>SUM(G9:J9)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="7">
         <f>SUM(F9+K9)</f>
@@ -4722,44 +6130,38 @@
       <c r="A10" s="8">
         <v>2</v>
       </c>
-      <c r="B10" s="21">
-        <v>1</v>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="24"/>
       <c r="F10" s="17">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="15">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="B11" s="21">
-        <v>5</v>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="24"/>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="25"/>
@@ -4771,63 +6173,63 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>4</v>
       </c>
-      <c r="B12" s="21">
-        <v>1</v>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="24"/>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G12" s="30">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="J12" s="25"/>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>5</v>
       </c>
-      <c r="B13" s="21"/>
+      <c r="B13" s="21">
+        <v>2</v>
+      </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="24"/>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="25">
+        <v>1</v>
+      </c>
       <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4859,25 +6261,29 @@
       <c r="A15" s="8">
         <v>7</v>
       </c>
-      <c r="B15" s="21"/>
+      <c r="B15" s="21">
+        <v>3</v>
+      </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="30"/>
+        <v>3</v>
+      </c>
+      <c r="G15" s="30">
+        <v>7</v>
+      </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
       <c r="J15" s="30"/>
       <c r="K15" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4892,17 +6298,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="30">
+        <v>12</v>
+      </c>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="J16" s="30"/>
       <c r="K16" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4934,15 +6342,13 @@
       <c r="A18" s="8">
         <v>10</v>
       </c>
-      <c r="B18" s="21">
-        <v>10</v>
-      </c>
+      <c r="B18" s="21"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
       <c r="E18" s="24"/>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="25"/>
@@ -4954,7 +6360,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4986,13 +6392,17 @@
       <c r="A20" s="8">
         <v>12</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
+      <c r="D20" s="25">
+        <v>2</v>
+      </c>
       <c r="E20" s="24"/>
       <c r="F20" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="25"/>
@@ -5004,7 +6414,7 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5036,13 +6446,15 @@
       <c r="A22" s="8">
         <v>14</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="21">
+        <v>1</v>
+      </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
       <c r="E22" s="24"/>
       <c r="F22" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="25"/>
@@ -5054,32 +6466,38 @@
       </c>
       <c r="L22" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>15</v>
       </c>
-      <c r="B23" s="21"/>
+      <c r="B23" s="21">
+        <v>1</v>
+      </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="24"/>
       <c r="F23" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="25"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25">
+        <v>1</v>
+      </c>
       <c r="I23" s="25"/>
       <c r="J23" s="30"/>
       <c r="K23" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5087,28 +6505,26 @@
         <v>16</v>
       </c>
       <c r="B24" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G24" s="30">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G24" s="30"/>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
       <c r="J24" s="30"/>
       <c r="K24" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5150,30 +6566,30 @@
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="I26" s="25">
+        <v>1</v>
+      </c>
       <c r="J26" s="30"/>
       <c r="K26" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>19</v>
       </c>
-      <c r="B27" s="21">
-        <v>1</v>
-      </c>
+      <c r="B27" s="21"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
       <c r="E27" s="24"/>
       <c r="F27" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="30"/>
       <c r="H27" s="25"/>
@@ -5185,7 +6601,7 @@
       </c>
       <c r="L27" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5225,30 +6641,34 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="30"/>
+      <c r="G29" s="30">
+        <v>9</v>
+      </c>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="J29" s="30"/>
       <c r="K29" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>22</v>
       </c>
-      <c r="B30" s="21"/>
+      <c r="B30" s="21">
+        <v>4</v>
+      </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="E30" s="24"/>
       <c r="F30" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G30" s="30"/>
       <c r="H30" s="25"/>
@@ -5260,7 +6680,7 @@
       </c>
       <c r="L30" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5268,14 +6688,14 @@
         <v>23</v>
       </c>
       <c r="B31" s="21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="25"/>
@@ -5287,7 +6707,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5319,27 +6739,27 @@
       <c r="A33" s="8">
         <v>25</v>
       </c>
-      <c r="B33" s="21">
-        <v>2</v>
-      </c>
+      <c r="B33" s="21"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="E33" s="24"/>
       <c r="F33" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G33" s="30"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="30">
+        <v>10</v>
+      </c>
       <c r="H33" s="25"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
       <c r="K33" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5347,26 +6767,22 @@
         <v>26</v>
       </c>
       <c r="B34" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" s="25"/>
-      <c r="D34" s="25">
-        <v>2</v>
-      </c>
+      <c r="D34" s="25"/>
       <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G34" s="30">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G34" s="30"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
       <c r="K34" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
@@ -5377,38 +6793,44 @@
       <c r="A35" s="8">
         <v>27</v>
       </c>
-      <c r="B35" s="21"/>
+      <c r="B35" s="21">
+        <v>1</v>
+      </c>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="E35" s="24"/>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="40"/>
-      <c r="H35" s="25"/>
+      <c r="H35" s="25">
+        <v>1</v>
+      </c>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
       <c r="K35" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>28</v>
       </c>
-      <c r="B36" s="21"/>
+      <c r="B36" s="21">
+        <v>3</v>
+      </c>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="E36" s="24"/>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="30"/>
       <c r="H36" s="25"/>
@@ -5420,7 +6842,7 @@
       </c>
       <c r="L36" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5429,38 +6851,40 @@
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="25">
-        <v>1</v>
-      </c>
+      <c r="D37" s="25"/>
       <c r="E37" s="24"/>
       <c r="F37" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G37" s="30"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30">
+        <v>3</v>
+      </c>
       <c r="H37" s="25"/>
       <c r="I37" s="25"/>
       <c r="J37" s="25"/>
       <c r="K37" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>30</v>
       </c>
-      <c r="B38" s="21"/>
+      <c r="B38" s="21">
+        <v>2</v>
+      </c>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="24"/>
       <c r="F38" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="30"/>
       <c r="H38" s="25"/>
@@ -5472,43 +6896,39 @@
       </c>
       <c r="L38" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>31</v>
       </c>
-      <c r="B39" s="26">
-        <v>3</v>
-      </c>
+      <c r="B39" s="26"/>
       <c r="C39" s="44"/>
       <c r="D39" s="44"/>
       <c r="E39" s="50"/>
       <c r="F39" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G39" s="30">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
       <c r="H39" s="25"/>
       <c r="I39" s="25"/>
       <c r="J39" s="25"/>
       <c r="K39" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -5516,7 +6936,7 @@
       </c>
       <c r="D40" s="46">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
@@ -5524,19 +6944,19 @@
       </c>
       <c r="F40" s="45">
         <f>SUM(F9:F39)</f>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="16">
         <f t="shared" si="4"/>
@@ -5544,11 +6964,11 @@
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5593,7 +7013,7 @@
       <c r="E43" s="70"/>
       <c r="F43" s="70"/>
       <c r="G43" s="71">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="H43" s="72"/>
       <c r="I43" s="73"/>
@@ -5611,7 +7031,7 @@
       <c r="E44" s="70"/>
       <c r="F44" s="70"/>
       <c r="G44" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="76"/>
       <c r="I44" s="75"/>
@@ -5648,7 +7068,7 @@
       <c r="F46" s="70"/>
       <c r="G46" s="81">
         <f>L40+G45</f>
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="H46" s="76"/>
       <c r="I46" s="75"/>
@@ -5667,7 +7087,7 @@
       <c r="F47" s="70"/>
       <c r="G47" s="81">
         <f>G43+G44-G46</f>
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="H47" s="76"/>
       <c r="I47" s="75"/>
@@ -5685,7 +7105,7 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="75">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="H48" s="76"/>
       <c r="I48" s="75"/>
@@ -5704,7 +7124,7 @@
       <c r="F49" s="70"/>
       <c r="G49" s="82">
         <f>G47-G48</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H49" s="83"/>
       <c r="I49" s="84"/>
@@ -5733,7 +7153,22 @@
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5782,9 +7217,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39B34D2-8B86-4C57-A168-32452A755D66}">
-  <dimension ref="A1:L56"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF150D4-1E58-46AE-A24B-2DF70BC2C7B6}">
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -5861,7 +7296,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55"/>
@@ -5951,15 +7386,13 @@
       <c r="A9" s="6">
         <v>1</v>
       </c>
-      <c r="B9" s="18">
-        <v>3</v>
-      </c>
+      <c r="B9" s="18"/>
       <c r="C9" s="48"/>
       <c r="D9" s="48"/>
       <c r="E9" s="49"/>
       <c r="F9" s="17">
         <f>SUM(B9:E9)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="41"/>
       <c r="H9" s="47"/>
@@ -5971,20 +7404,22 @@
       </c>
       <c r="L9" s="7">
         <f>SUM(F9+K9)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>2</v>
       </c>
-      <c r="B10" s="21"/>
+      <c r="B10" s="21">
+        <v>1</v>
+      </c>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="24"/>
       <c r="F10" s="17">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="25"/>
@@ -5996,7 +7431,7 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6006,22 +7441,28 @@
       <c r="B11" s="21"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
-      <c r="E11" s="24"/>
+      <c r="E11" s="24">
+        <v>1</v>
+      </c>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="30">
+        <v>1</v>
+      </c>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
+      <c r="J11" s="25">
+        <v>1</v>
+      </c>
       <c r="K11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6037,60 +7478,60 @@
         <v>0</v>
       </c>
       <c r="G12" s="30"/>
-      <c r="H12" s="25"/>
+      <c r="H12" s="25">
+        <v>1</v>
+      </c>
       <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
+      <c r="J12" s="25">
+        <v>1</v>
+      </c>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>5</v>
       </c>
-      <c r="B13" s="21">
-        <v>2</v>
-      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="24"/>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G13" s="30">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30"/>
       <c r="H13" s="25"/>
-      <c r="I13" s="25">
-        <v>1</v>
-      </c>
+      <c r="I13" s="25"/>
       <c r="J13" s="25"/>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>6</v>
       </c>
-      <c r="B14" s="21"/>
+      <c r="B14" s="21">
+        <v>15</v>
+      </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
       <c r="E14" s="24"/>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G14" s="30"/>
       <c r="H14" s="25"/>
@@ -6102,36 +7543,32 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>7</v>
       </c>
-      <c r="B15" s="21">
-        <v>3</v>
-      </c>
+      <c r="B15" s="21"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G15" s="30">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
       <c r="J15" s="30"/>
       <c r="K15" s="15">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6146,19 +7583,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="30">
-        <v>12</v>
-      </c>
+      <c r="G16" s="30"/>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="J16" s="30"/>
       <c r="K16" s="15">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6173,17 +7608,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="30"/>
+      <c r="G17" s="30">
+        <v>1</v>
+      </c>
       <c r="H17" s="25"/>
       <c r="I17" s="25"/>
       <c r="J17" s="30"/>
       <c r="K17" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6240,17 +7677,13 @@
       <c r="A20" s="8">
         <v>12</v>
       </c>
-      <c r="B20" s="21">
-        <v>2</v>
-      </c>
+      <c r="B20" s="21"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="25">
-        <v>2</v>
-      </c>
+      <c r="D20" s="25"/>
       <c r="E20" s="24"/>
       <c r="F20" s="17">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="25"/>
@@ -6262,20 +7695,24 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>13</v>
       </c>
-      <c r="B21" s="21"/>
+      <c r="B21" s="21">
+        <v>6</v>
+      </c>
       <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
+      <c r="D21" s="25">
+        <v>2</v>
+      </c>
       <c r="E21" s="24"/>
       <c r="F21" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G21" s="30"/>
       <c r="H21" s="25"/>
@@ -6287,22 +7724,20 @@
       </c>
       <c r="L21" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>14</v>
       </c>
-      <c r="B22" s="21">
-        <v>1</v>
-      </c>
+      <c r="B22" s="21"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
       <c r="E22" s="24"/>
       <c r="F22" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="25"/>
@@ -6314,53 +7749,45 @@
       </c>
       <c r="L22" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>15</v>
       </c>
-      <c r="B23" s="21">
-        <v>1</v>
-      </c>
+      <c r="B23" s="21"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="24"/>
       <c r="F23" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G23" s="30">
-        <v>1</v>
-      </c>
-      <c r="H23" s="25">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="25"/>
       <c r="I23" s="25"/>
       <c r="J23" s="30"/>
       <c r="K23" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>16</v>
       </c>
-      <c r="B24" s="21">
-        <v>2</v>
-      </c>
+      <c r="B24" s="21"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="24"/>
       <c r="F24" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="30"/>
       <c r="H24" s="25"/>
@@ -6372,7 +7799,7 @@
       </c>
       <c r="L24" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6414,17 +7841,15 @@
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="25"/>
-      <c r="I26" s="25">
-        <v>1</v>
-      </c>
+      <c r="I26" s="25"/>
       <c r="J26" s="30"/>
       <c r="K26" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6489,34 +7914,36 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="30">
-        <v>9</v>
-      </c>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25">
+        <v>1</v>
+      </c>
+      <c r="I29" s="25">
+        <v>1</v>
+      </c>
+      <c r="J29" s="30">
+        <v>2</v>
+      </c>
       <c r="K29" s="15">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>22</v>
       </c>
-      <c r="B30" s="21">
-        <v>4</v>
-      </c>
+      <c r="B30" s="21"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="E30" s="24"/>
       <c r="F30" s="17">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G30" s="30"/>
       <c r="H30" s="25"/>
@@ -6528,22 +7955,20 @@
       </c>
       <c r="L30" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>23</v>
       </c>
-      <c r="B31" s="21">
-        <v>1</v>
-      </c>
+      <c r="B31" s="21"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="E31" s="24"/>
       <c r="F31" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="25"/>
@@ -6555,7 +7980,7 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6595,19 +8020,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G33" s="30">
-        <v>10</v>
-      </c>
+      <c r="G33" s="30"/>
       <c r="H33" s="25"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
       <c r="K33" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6615,14 +8038,14 @@
         <v>26</v>
       </c>
       <c r="B34" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="E34" s="24"/>
       <c r="F34" s="17">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" s="30"/>
       <c r="H34" s="25"/>
@@ -6634,51 +8057,45 @@
       </c>
       <c r="L34" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>27</v>
       </c>
-      <c r="B35" s="21">
-        <v>1</v>
-      </c>
+      <c r="B35" s="21"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="E35" s="24"/>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="40"/>
-      <c r="H35" s="25">
-        <v>1</v>
-      </c>
+      <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
       <c r="K35" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>28</v>
       </c>
-      <c r="B36" s="21">
-        <v>3</v>
-      </c>
+      <c r="B36" s="21"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="E36" s="24"/>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36" s="30"/>
       <c r="H36" s="25"/>
@@ -6690,7 +8107,7 @@
       </c>
       <c r="L36" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6705,34 +8122,30 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G37" s="30">
-        <v>3</v>
-      </c>
+      <c r="G37" s="30"/>
       <c r="H37" s="25"/>
       <c r="I37" s="25"/>
       <c r="J37" s="25"/>
       <c r="K37" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>30</v>
       </c>
-      <c r="B38" s="21">
-        <v>2</v>
-      </c>
+      <c r="B38" s="21"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="24"/>
       <c r="F38" s="17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="30"/>
       <c r="H38" s="25"/>
@@ -6744,7 +8157,7 @@
       </c>
       <c r="L38" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6776,7 +8189,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="46">
         <f>SUM(B9:B39)</f>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -6788,15 +8201,15 @@
       </c>
       <c r="E40" s="46">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="45">
         <f>SUM(F9:F39)</f>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G40" s="16">
         <f>SUM(G9:G39)</f>
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -6804,19 +8217,19 @@
       </c>
       <c r="I40" s="16">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K40" s="16">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6861,7 +8274,7 @@
       <c r="E43" s="70"/>
       <c r="F43" s="70"/>
       <c r="G43" s="71">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="H43" s="72"/>
       <c r="I43" s="73"/>
@@ -6879,7 +8292,7 @@
       <c r="E44" s="70"/>
       <c r="F44" s="70"/>
       <c r="G44" s="75">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H44" s="76"/>
       <c r="I44" s="75"/>
@@ -6916,7 +8329,7 @@
       <c r="F46" s="70"/>
       <c r="G46" s="81">
         <f>L40+G45</f>
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="H46" s="76"/>
       <c r="I46" s="75"/>
@@ -6935,7 +8348,7 @@
       <c r="F47" s="70"/>
       <c r="G47" s="81">
         <f>G43+G44-G46</f>
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H47" s="76"/>
       <c r="I47" s="75"/>
@@ -6953,7 +8366,7 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="75">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="H48" s="76"/>
       <c r="I48" s="75"/>
@@ -6972,7 +8385,7 @@
       <c r="F49" s="70"/>
       <c r="G49" s="82">
         <f>G47-G48</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H49" s="83"/>
       <c r="I49" s="84"/>
@@ -7001,22 +8414,27 @@
     <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5E97EB-A93F-4497-871D-BA515F60CEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B542ADB-0629-46FE-B222-2DB79F78CDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="34" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="MARS 2026" sheetId="36" r:id="rId3"/>
     <sheet name="AVRIL 2026" sheetId="37" r:id="rId4"/>
     <sheet name="MAI 2026" sheetId="38" r:id="rId5"/>
+    <sheet name="Juin 2026" sheetId="39" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -204,6 +205,12 @@
   </si>
   <si>
     <t>06 Compteurs : 2 (DN 15/21) , 1 (DN 100) ,1 (DN 80), 1 (DN 65) , 1 (DN 50)  Destination Antenne Robea</t>
+  </si>
+  <si>
+    <t>Mois de JUIN 2026</t>
+  </si>
+  <si>
+    <t>01 Compteurs DN 80 Destination Seghouane</t>
   </si>
 </sst>
 </file>
@@ -1053,14 +1060,67 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1095,67 +1155,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1843,6 +1850,139 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC2786F-FD9B-43D1-A972-2B2BC3307CB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -2139,48 +2279,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -2191,36 +2331,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -2232,36 +2372,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="63" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -2292,7 +2432,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="64"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -3167,149 +3307,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="68"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="71">
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
         <v>447</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="75">
-        <v>0</v>
-      </c>
-      <c r="H44" s="76"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="76"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="78">
-        <v>0</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="80"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="81">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
         <v>96</v>
       </c>
-      <c r="H46" s="76"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="76"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="81">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
         <v>351</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="75">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
         <v>321</v>
       </c>
-      <c r="H48" s="76"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="76"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="82">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
         <v>30</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="83"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -3413,48 +3553,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -3465,36 +3605,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -3506,36 +3646,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="63" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -3566,7 +3706,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="64"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -4453,149 +4593,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="68"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="71">
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
         <v>321</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="75">
-        <v>0</v>
-      </c>
-      <c r="H44" s="76"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="76"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="78">
-        <v>0</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="80"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="81">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
         <v>104</v>
       </c>
-      <c r="H46" s="76"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="76"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="81">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
         <v>217</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="75">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
         <v>214</v>
       </c>
-      <c r="H48" s="76"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="76"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="82">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
         <v>3</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="83"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -4684,48 +4824,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -4736,36 +4876,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -4777,36 +4917,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="63" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -4837,7 +4977,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="64"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -5718,149 +5858,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="68"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="71">
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
         <v>214</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="75">
-        <v>0</v>
-      </c>
-      <c r="H44" s="76"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="76"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="78">
-        <v>0</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="80"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="81">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
         <v>44</v>
       </c>
-      <c r="H46" s="76"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="76"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="81">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
         <v>170</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="75">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
         <v>169</v>
       </c>
-      <c r="H48" s="76"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="76"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="82">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
         <v>1</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="83"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -5944,48 +6084,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -5996,36 +6136,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -6037,36 +6177,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="63" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -6097,7 +6237,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="64"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -6986,149 +7126,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="68"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="71">
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
         <v>169</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="75">
-        <v>1</v>
-      </c>
-      <c r="H44" s="76"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="76"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>1</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="78">
-        <v>0</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="80"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="81">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
         <v>80</v>
       </c>
-      <c r="H46" s="76"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="76"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="81">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
         <v>90</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="75">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
         <v>78</v>
       </c>
-      <c r="H48" s="76"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="76"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="82">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
         <v>12</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="83"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -7227,48 +7367,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="31"/>
       <c r="F1" s="32"/>
-      <c r="G1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="31"/>
       <c r="F2" s="32"/>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="31"/>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -7279,36 +7419,36 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -7320,36 +7460,36 @@
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
       <c r="J6" s="12"/>
       <c r="K6" s="33"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="63" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="34" t="s">
         <v>11</v>
       </c>
@@ -7380,7 +7520,7 @@
       <c r="K8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="64"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
@@ -8247,149 +8387,149 @@
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67" t="s">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="68"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="11"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="71">
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
         <v>78</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="11"/>
       <c r="L43" s="13"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="75">
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
         <v>35</v>
       </c>
-      <c r="H44" s="76"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="76"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="11"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="78">
-        <v>0</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="80"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
       <c r="K45" s="11"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="81">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
         <f>L40+G45</f>
         <v>35</v>
       </c>
-      <c r="H46" s="76"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="76"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="11"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="81">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
         <f>G43+G44-G46</f>
         <v>78</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="11"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="75">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
         <v>61</v>
       </c>
-      <c r="H48" s="76"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="76"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="11"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="82">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
         <f>G47-G48</f>
         <v>17</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="83"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="11"/>
       <c r="L49" s="3"/>
     </row>
@@ -8481,4 +8621,1244 @@
   <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{166BB1E5-D117-4942-B6E6-8CE0BCAB38BB}">
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="41">
+        <v>1</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47">
+        <v>2</v>
+      </c>
+      <c r="J9" s="47"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>3</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30">
+        <v>2</v>
+      </c>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="30">
+        <v>3</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25">
+        <v>1</v>
+      </c>
+      <c r="E21" s="24"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21">
+        <v>1</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="30"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21">
+        <v>2</v>
+      </c>
+      <c r="C32" s="25">
+        <v>1</v>
+      </c>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40">
+        <v>1</v>
+      </c>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21">
+        <v>13</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>17</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>19</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>7</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="67"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>61</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>104</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
+        <f>L40+G45</f>
+        <v>28</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
+        <f>G43+G44-G46</f>
+        <v>137</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>136</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
+        <f>G47-G48</f>
+        <v>1</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Fiche de Stock 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B542ADB-0629-46FE-B222-2DB79F78CDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB337AC-A4DF-4C42-BF76-09228D313453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="34" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="AVRIL 2026" sheetId="37" r:id="rId4"/>
     <sheet name="MAI 2026" sheetId="38" r:id="rId5"/>
     <sheet name="Juin 2026" sheetId="39" r:id="rId6"/>
+    <sheet name="Juillet 2026" sheetId="40" r:id="rId7"/>
+    <sheet name="Aout 2026" sheetId="41" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="54">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -211,6 +213,15 @@
   </si>
   <si>
     <t>01 Compteurs DN 80 Destination Seghouane</t>
+  </si>
+  <si>
+    <t>Mois de JUILLET 2026</t>
+  </si>
+  <si>
+    <t>05 Compteurs DN 15/21 Destination Tlathet Douairs</t>
+  </si>
+  <si>
+    <t>Mois de AOUT 2026</t>
   </si>
 </sst>
 </file>
@@ -1983,6 +1994,272 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A92DCE8F-D89D-4744-9839-EC1BCE96B4A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{370B73A8-822B-46C9-9D51-6261FCBE8A39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5610225" y="8210550"/>
+          <a:ext cx="958850" cy="1139825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -9861,4 +10138,2457 @@
   <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DC6B94-475F-4BBD-A031-80A440D6F908}">
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="41"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21">
+        <v>2</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24">
+        <v>1</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21">
+        <v>4</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21">
+        <v>1</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21">
+        <v>1</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21">
+        <v>3</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G30" s="30"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21">
+        <v>12</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21">
+        <v>7</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25">
+        <v>2</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21">
+        <v>5</v>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21">
+        <v>6</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>41</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>44</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="67"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>136</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>0</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
+        <f>L40+G45</f>
+        <v>44</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
+        <f>G43+G44-G46</f>
+        <v>92</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>87</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
+        <f>G47-G48</f>
+        <v>5</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC23FFA0-F96C-4640-9A86-15F748383A76}">
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="1:12" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="17">
+        <f>SUM(B9:E9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="41"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="15">
+        <f>SUM(G9:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <f>SUM(F9+K9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="17">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>11</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="30"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>12</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>16</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>17</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>21</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>22</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="30"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>23</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>25</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="30"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>28</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>29</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>31</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="46">
+        <f>SUM(B9:B39)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>SUM(F9:F39)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="16">
+        <f>SUM(G9:G39)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="67"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="62">
+        <v>87</v>
+      </c>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53">
+        <v>150</v>
+      </c>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="60">
+        <v>0</v>
+      </c>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14"/>
+      <c r="B46" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="58">
+        <f>L40+G45</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="58">
+        <f>G43+G44-G46</f>
+        <v>237</v>
+      </c>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53">
+        <v>87</v>
+      </c>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="55">
+        <f>G47-G48</f>
+        <v>150</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="38"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>